--- a/programs/_template/program.xlsx
+++ b/programs/_template/program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/20baf977624bf256/Documents/GitHub/MondayProgramSync/MondayProgramSync/programs/_template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AC50BD816249BE4DAB5462567E27A33B0D7485FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFA359CE-B897-4084-BE98-9ECA25BAAF83}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_AC50BD816249BE4DAB5462567E27A33B0D7485FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AF831C3-4DB8-49F0-ACBF-68C3BF898294}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Legend" sheetId="1" r:id="rId1"/>
@@ -1714,7 +1714,7 @@
         <v>166</v>
       </c>
       <c r="C5" s="23">
-        <v>45870</v>
+        <v>46127</v>
       </c>
       <c r="D5" s="62" t="s">
         <v>167</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C7" s="23">
         <f>$C$5+10</f>
-        <v>45880</v>
+        <v>46137</v>
       </c>
       <c r="D7" s="64" t="s">
         <v>172</v>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="C5" s="42">
         <f>Legend!$C$5+1</f>
-        <v>45871</v>
+        <v>46128</v>
       </c>
       <c r="D5" s="42" t="s">
         <v>11</v>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C6" s="42">
         <f>Legend!$C$5+2</f>
-        <v>45872</v>
+        <v>46129</v>
       </c>
       <c r="D6" s="42" t="s">
         <v>11</v>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="C7" s="43">
         <f>Legend!$C$5+7</f>
-        <v>45877</v>
+        <v>46134</v>
       </c>
       <c r="D7" s="43" t="s">
         <v>11</v>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C8" s="43">
         <f>Legend!$C$5+9</f>
-        <v>45879</v>
+        <v>46136</v>
       </c>
       <c r="D8" s="43" t="s">
         <v>11</v>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="C9" s="44">
         <f>Legend!$C$7</f>
-        <v>45880</v>
+        <v>46137</v>
       </c>
       <c r="D9" s="44" t="s">
         <v>11</v>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="C10" s="44">
         <f>Legend!$C$7</f>
-        <v>45880</v>
+        <v>46137</v>
       </c>
       <c r="D10" s="44" t="s">
         <v>11</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C11" s="45">
         <f>Legend!$C$7+10</f>
-        <v>45890</v>
+        <v>46147</v>
       </c>
       <c r="D11" s="45" t="s">
         <v>11</v>
